--- a/artfynd/A 29277-2026 artfynd.xlsx
+++ b/artfynd/A 29277-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74636571</v>
+        <v>135419443</v>
       </c>
       <c r="B2" t="n">
-        <v>57132</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ryggmossens NR, Upl</t>
+          <t>Ryggmossen SV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629325</v>
+        <v>629206</v>
       </c>
       <c r="R2" t="n">
-        <v>6658290</v>
+        <v>6658274</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-12-09</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-12-09</t>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,24 +775,1656 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135419443</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135419446</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97511</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>629175</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6658298</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419446</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135419432</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629203</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6658168</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419432</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135419434</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>629194</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6658170</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419434</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135419435</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>629144</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6658174</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419435</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135419436</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>629117</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6658197</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419436</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135419437</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>629164</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6658218</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419437</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135419439</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>629195</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6658205</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419439</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135419445</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92048</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>629204</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6658298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419445</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135419438</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>629201</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6658203</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419438</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135419440</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>629179</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6658218</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419440</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74636571</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ryggmossens NR, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>629325</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6658290</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2008-12-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2008-12-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/74636571</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135419442</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>629179</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6658218</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419442</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135419433</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106411</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ryggmossen SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>629203</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6658172</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135419433</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29277-2026 artfynd.xlsx
+++ b/artfynd/A 29277-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135419443</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135419446</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135419432</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>135419434</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135419435</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135419436</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135419437</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135419439</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>135419445</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135419438</v>
       </c>
       <c r="B11" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135419433</v>
       </c>
       <c r="B15" t="n">
-        <v>106411</v>
+        <v>106413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29277-2026 artfynd.xlsx
+++ b/artfynd/A 29277-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135419443</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135419446</v>
       </c>
       <c r="B3" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135419432</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
         <v>135419434</v>
       </c>
       <c r="B5" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135419435</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135419436</v>
       </c>
       <c r="B7" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135419437</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135419439</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>135419445</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>135419438</v>
       </c>
       <c r="B11" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135419440</v>
       </c>
       <c r="B12" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>135419442</v>
       </c>
       <c r="B14" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135419433</v>
       </c>
       <c r="B15" t="n">
-        <v>106413</v>
+        <v>106433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
